--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260902.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260902.xlsx
@@ -843,17 +843,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>11,514,346</t>
+          <t>7,436,703</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>7,436,703</t>
+          <t>11,514,346</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,281,360</t>
+          <t>266,794,404</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>266,794,404</t>
+          <t>1,281,360</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>216,204,308</t>
+          <t>7,991,377</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>7,991,377</t>
+          <t>216,204,308</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
